--- a/Source Data/Source Data Fig. 3.xlsx
+++ b/Source Data/Source Data Fig. 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nusu-my.sharepoint.com/personal/khudiyev_nus_edu_sg/Documents/PUBLICATIONS/PUBLISHED/Fiber Computer/Nature/Pre-Acceptance_Revision/Source Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24882713-7C37-42D1-908B-8150BEADC4ED}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{548CC7E3-1D8D-410A-83F9-66C778B83176}"/>
   <bookViews>
-    <workbookView xWindow="4790" yWindow="4720" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4790" yWindow="4720" windowWidth="28800" windowHeight="15370" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 3d" sheetId="1" r:id="rId1"/>
@@ -42,51 +42,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Time (h)</t>
   </si>
   <si>
-    <t>Denim fabric (kg m⁻²)</t>
+    <t>Cumulative water vapor transmission (kg m⁻²)</t>
   </si>
   <si>
-    <t>Cotton fabric (kg m⁻²)</t>
+    <t xml:space="preserve">Denim fabric </t>
   </si>
   <si>
-    <t>Polyester fabric (kg m⁻²)</t>
+    <t xml:space="preserve">Cotton fabric </t>
   </si>
   <si>
-    <t>Pixel fibre fabric (kg m⁻²)</t>
+    <t xml:space="preserve">Polyester fabric </t>
+  </si>
+  <si>
+    <t>Pixel fibre fabric</t>
   </si>
   <si>
     <t>Washing cycles</t>
   </si>
   <si>
-    <t>Bending cycles</t>
-  </si>
-  <si>
     <t>Illuminance 1 (lux)</t>
   </si>
   <si>
-    <t>Illuminance 2</t>
+    <t>Illuminance 2 (lux)</t>
   </si>
   <si>
-    <t>Illuminance 3</t>
+    <t>Illuminance 3 (lux)</t>
   </si>
   <si>
-    <t>Mean</t>
+    <t>Mean (lux)</t>
   </si>
   <si>
-    <t>SD</t>
+    <t>SD (lux)</t>
   </si>
   <si>
     <t>Resistance 1 (kΩ)</t>
   </si>
   <si>
-    <t>Resistance 2</t>
+    <t>Resistance 2 (kΩ)</t>
   </si>
   <si>
-    <t>Resistance 3</t>
+    <t>Resistance 3 (kΩ)</t>
+  </si>
+  <si>
+    <t>Mean (kΩ)</t>
+  </si>
+  <si>
+    <t>SD (kΩ)</t>
+  </si>
+  <si>
+    <t>Bending cycles</t>
   </si>
   <si>
     <t>Time (us)</t>
@@ -99,6 +108,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -150,13 +162,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -171,14 +191,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -216,7 +232,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -322,7 +338,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -464,7 +480,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -472,420 +488,439 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
+  <cols>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="27.625" customWidth="1"/>
+    <col min="4" max="4" width="22.5" customWidth="1"/>
+    <col min="5" max="5" width="24.125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:7" ht="14.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+    <row r="2" spans="1:7" ht="14.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="14.25">
       <c r="A3">
-        <v>2.7166700000000001</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>4.2439999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>2.8289999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2.8289999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5.6590000000000001E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>7.55</v>
-      </c>
-      <c r="B4">
-        <v>0.55174000000000001</v>
-      </c>
-      <c r="C4">
-        <v>0.33953</v>
-      </c>
-      <c r="D4">
-        <v>0.36781999999999998</v>
-      </c>
-      <c r="E4">
-        <v>0.55174000000000001</v>
+        <v>2.7166700000000001</v>
+      </c>
+      <c r="B4" s="4">
+        <v>4.2439999999999999E-2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>2.8289999999999999E-2</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2.8289999999999999E-2</v>
+      </c>
+      <c r="E4" s="4">
+        <v>5.6590000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>9.5500000000000007</v>
-      </c>
-      <c r="B5">
-        <v>0.72150000000000003</v>
-      </c>
-      <c r="C5">
-        <v>0.45271</v>
-      </c>
-      <c r="D5">
-        <v>0.52344000000000002</v>
-      </c>
-      <c r="E5">
-        <v>0.76393999999999995</v>
+        <v>7.55</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.55174000000000001</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.33953</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.36781999999999998</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.55174000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21.55</v>
-      </c>
-      <c r="B6">
-        <v>1.7825299999999999</v>
-      </c>
-      <c r="C6">
-        <v>1.0893299999999999</v>
-      </c>
-      <c r="D6">
-        <v>1.28739</v>
-      </c>
-      <c r="E6">
-        <v>1.92401</v>
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.72150000000000003</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.45271</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.52344000000000002</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.76393999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>25.55</v>
-      </c>
-      <c r="B7">
-        <v>2.20695</v>
-      </c>
-      <c r="C7">
-        <v>1.3298300000000001</v>
-      </c>
-      <c r="D7">
-        <v>1.57033</v>
-      </c>
-      <c r="E7">
-        <v>2.3059799999999999</v>
+        <v>21.55</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1.7825299999999999</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.0893299999999999</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.28739</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1.92401</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>27.55</v>
-      </c>
-      <c r="B8">
-        <v>2.34842</v>
-      </c>
-      <c r="C8">
-        <v>1.4147099999999999</v>
-      </c>
-      <c r="D8">
-        <v>1.6835</v>
-      </c>
-      <c r="E8">
-        <v>2.4615999999999998</v>
+        <v>25.55</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2.20695</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1.3298300000000001</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1.57033</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2.3059799999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>29.55</v>
-      </c>
-      <c r="B9">
-        <v>2.4757400000000001</v>
-      </c>
-      <c r="C9">
-        <v>1.52789</v>
-      </c>
-      <c r="D9">
-        <v>1.85327</v>
-      </c>
-      <c r="E9">
-        <v>2.6313599999999999</v>
+        <v>27.55</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2.34842</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1.4147099999999999</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1.6835</v>
+      </c>
+      <c r="E9" s="4">
+        <v>2.4615999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>31.55</v>
-      </c>
-      <c r="B10">
-        <v>2.6738</v>
-      </c>
-      <c r="C10">
-        <v>1.6976500000000001</v>
-      </c>
-      <c r="D10">
-        <v>2.0088900000000001</v>
-      </c>
-      <c r="E10">
-        <v>2.8294199999999998</v>
+        <v>29.55</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2.4757400000000001</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1.52789</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1.85327</v>
+      </c>
+      <c r="E10" s="4">
+        <v>2.6313599999999999</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>33.549999999999997</v>
-      </c>
-      <c r="B11">
-        <v>2.8152699999999999</v>
-      </c>
-      <c r="C11">
-        <v>1.82498</v>
-      </c>
-      <c r="D11">
-        <v>2.1220699999999999</v>
-      </c>
-      <c r="E11">
-        <v>2.99919</v>
+        <v>31.55</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2.6738</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1.6976500000000001</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2.0088900000000001</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2.8294199999999998</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>47.55</v>
-      </c>
-      <c r="B12">
-        <v>3.8480099999999999</v>
-      </c>
-      <c r="C12">
-        <v>2.5889199999999999</v>
-      </c>
-      <c r="D12">
-        <v>2.9426000000000001</v>
-      </c>
-      <c r="E12">
-        <v>4.0177800000000001</v>
+        <v>33.549999999999997</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2.8152699999999999</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1.82498</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2.1220699999999999</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2.99919</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>49.55</v>
-      </c>
-      <c r="B13">
-        <v>4.0460700000000003</v>
-      </c>
-      <c r="C13">
-        <v>2.75868</v>
-      </c>
-      <c r="D13">
-        <v>3.0699200000000002</v>
-      </c>
-      <c r="E13">
-        <v>4.0460700000000003</v>
+        <v>47.55</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3.8480099999999999</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2.5889199999999999</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2.9426000000000001</v>
+      </c>
+      <c r="E13" s="4">
+        <v>4.0177800000000001</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>51.55</v>
-      </c>
-      <c r="B14">
-        <v>4.2299800000000003</v>
-      </c>
-      <c r="C14">
-        <v>2.8860100000000002</v>
-      </c>
-      <c r="D14">
-        <v>3.1972399999999999</v>
-      </c>
-      <c r="E14">
-        <v>4.21584</v>
+        <v>49.55</v>
+      </c>
+      <c r="B14" s="4">
+        <v>4.0460700000000003</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2.75868</v>
+      </c>
+      <c r="D14" s="4">
+        <v>3.0699200000000002</v>
+      </c>
+      <c r="E14" s="4">
+        <v>4.0460700000000003</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>71.55</v>
-      </c>
-      <c r="B15">
-        <v>5.6163999999999996</v>
-      </c>
-      <c r="C15">
-        <v>4.1168100000000001</v>
-      </c>
-      <c r="D15">
-        <v>4.4704800000000002</v>
-      </c>
-      <c r="E15">
-        <v>5.7012799999999997</v>
+        <v>51.55</v>
+      </c>
+      <c r="B15" s="4">
+        <v>4.2299800000000003</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2.8860100000000002</v>
+      </c>
+      <c r="D15" s="4">
+        <v>3.1972399999999999</v>
+      </c>
+      <c r="E15" s="4">
+        <v>4.21584</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>73.55</v>
-      </c>
-      <c r="B16">
-        <v>5.7578699999999996</v>
-      </c>
-      <c r="C16">
-        <v>4.2299800000000003</v>
-      </c>
-      <c r="D16">
-        <v>4.59781</v>
-      </c>
-      <c r="E16">
-        <v>5.8851899999999997</v>
+        <v>71.55</v>
+      </c>
+      <c r="B16" s="4">
+        <v>5.6163999999999996</v>
+      </c>
+      <c r="C16" s="4">
+        <v>4.1168100000000001</v>
+      </c>
+      <c r="D16" s="4">
+        <v>4.4704800000000002</v>
+      </c>
+      <c r="E16" s="4">
+        <v>5.7012799999999997</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>75.55</v>
-      </c>
-      <c r="B17">
-        <v>5.8993399999999996</v>
-      </c>
-      <c r="C17">
-        <v>4.3856000000000002</v>
-      </c>
-      <c r="D17">
-        <v>4.7534299999999998</v>
-      </c>
-      <c r="E17">
-        <v>6.0266599999999997</v>
+        <v>73.55</v>
+      </c>
+      <c r="B17" s="4">
+        <v>5.7578699999999996</v>
+      </c>
+      <c r="C17" s="4">
+        <v>4.2299800000000003</v>
+      </c>
+      <c r="D17" s="4">
+        <v>4.59781</v>
+      </c>
+      <c r="E17" s="4">
+        <v>5.8851899999999997</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>77.55</v>
-      </c>
-      <c r="B18">
-        <v>6.0691100000000002</v>
-      </c>
-      <c r="C18">
-        <v>4.5270700000000001</v>
-      </c>
-      <c r="D18">
-        <v>4.8666</v>
-      </c>
-      <c r="E18">
-        <v>6.1539900000000003</v>
+        <v>75.55</v>
+      </c>
+      <c r="B18" s="4">
+        <v>5.8993399999999996</v>
+      </c>
+      <c r="C18" s="4">
+        <v>4.3856000000000002</v>
+      </c>
+      <c r="D18" s="4">
+        <v>4.7534299999999998</v>
+      </c>
+      <c r="E18" s="4">
+        <v>6.0266599999999997</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>81.55</v>
-      </c>
-      <c r="B19">
-        <v>6.3661899999999996</v>
-      </c>
-      <c r="C19">
-        <v>4.7534299999999998</v>
-      </c>
-      <c r="D19">
-        <v>5.1636899999999999</v>
-      </c>
-      <c r="E19">
-        <v>6.4793700000000003</v>
+        <v>77.55</v>
+      </c>
+      <c r="B19" s="4">
+        <v>6.0691100000000002</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4.5270700000000001</v>
+      </c>
+      <c r="D19" s="4">
+        <v>4.8666</v>
+      </c>
+      <c r="E19" s="4">
+        <v>6.1539900000000003</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>93.55</v>
-      </c>
-      <c r="B20">
-        <v>7.2291699999999999</v>
-      </c>
-      <c r="C20">
-        <v>5.3475999999999999</v>
-      </c>
-      <c r="D20">
-        <v>5.8851899999999997</v>
-      </c>
-      <c r="E20">
-        <v>7.2857599999999998</v>
+        <v>81.55</v>
+      </c>
+      <c r="B20" s="4">
+        <v>6.3661899999999996</v>
+      </c>
+      <c r="C20" s="4">
+        <v>4.7534299999999998</v>
+      </c>
+      <c r="D20" s="4">
+        <v>5.1636899999999999</v>
+      </c>
+      <c r="E20" s="4">
+        <v>6.4793700000000003</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>95.55</v>
-      </c>
-      <c r="B21">
-        <v>7.35649</v>
-      </c>
-      <c r="C21">
-        <v>5.4890699999999999</v>
-      </c>
-      <c r="D21">
-        <v>6.0125200000000003</v>
-      </c>
-      <c r="E21">
-        <v>7.4555199999999999</v>
+        <v>93.55</v>
+      </c>
+      <c r="B21" s="4">
+        <v>7.2291699999999999</v>
+      </c>
+      <c r="C21" s="4">
+        <v>5.3475999999999999</v>
+      </c>
+      <c r="D21" s="4">
+        <v>5.8851899999999997</v>
+      </c>
+      <c r="E21" s="4">
+        <v>7.2857599999999998</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>97.55</v>
-      </c>
-      <c r="B22">
-        <v>7.4696699999999998</v>
-      </c>
-      <c r="C22">
-        <v>5.6305500000000004</v>
-      </c>
-      <c r="D22">
-        <v>6.1115500000000003</v>
-      </c>
-      <c r="E22">
-        <v>7.6111399999999998</v>
+        <v>95.55</v>
+      </c>
+      <c r="B22" s="4">
+        <v>7.35649</v>
+      </c>
+      <c r="C22" s="4">
+        <v>5.4890699999999999</v>
+      </c>
+      <c r="D22" s="4">
+        <v>6.0125200000000003</v>
+      </c>
+      <c r="E22" s="4">
+        <v>7.4555199999999999</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>100.05</v>
-      </c>
-      <c r="B23">
-        <v>7.6677299999999997</v>
-      </c>
-      <c r="C23">
-        <v>5.7437199999999997</v>
-      </c>
-      <c r="D23">
-        <v>6.2671700000000001</v>
-      </c>
-      <c r="E23">
-        <v>7.7808999999999999</v>
+        <v>97.55</v>
+      </c>
+      <c r="B23" s="4">
+        <v>7.4696699999999998</v>
+      </c>
+      <c r="C23" s="4">
+        <v>5.6305500000000004</v>
+      </c>
+      <c r="D23" s="4">
+        <v>6.1115500000000003</v>
+      </c>
+      <c r="E23" s="4">
+        <v>7.6111399999999998</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
+        <v>100.05</v>
+      </c>
+      <c r="B24" s="4">
+        <v>7.6677299999999997</v>
+      </c>
+      <c r="C24" s="4">
+        <v>5.7437199999999997</v>
+      </c>
+      <c r="D24" s="4">
+        <v>6.2671700000000001</v>
+      </c>
+      <c r="E24" s="4">
+        <v>7.7808999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
         <v>101.55</v>
       </c>
-      <c r="B24">
+      <c r="B25" s="4">
         <v>7.7243199999999996</v>
       </c>
-      <c r="C24">
+      <c r="C25" s="4">
         <v>5.8427499999999997</v>
       </c>
-      <c r="D24">
+      <c r="D25" s="4">
         <v>6.3661899999999996</v>
       </c>
-      <c r="E24">
+      <c r="E25" s="4">
         <v>7.8657899999999996</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:E1"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -894,28 +929,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2728C3D7-42E8-48EC-A13E-D9FC52D07AAA}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
+    <col min="2" max="2" width="16.625" customWidth="1"/>
+    <col min="3" max="3" width="19.875" customWidth="1"/>
+    <col min="4" max="4" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="14.25">
       <c r="A1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -923,19 +961,19 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>170.48</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>173.09</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>171.08</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>171.55</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>1.37</v>
       </c>
     </row>
@@ -943,19 +981,19 @@
       <c r="A3">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>167.85</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>169.8</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>171.75</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>169.8</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>1.95</v>
       </c>
     </row>
@@ -963,19 +1001,19 @@
       <c r="A4">
         <v>10</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>168.67</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>168.68</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>172.38</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>169.91</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>2.14</v>
       </c>
     </row>
@@ -983,19 +1021,19 @@
       <c r="A5">
         <v>15</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>169.44</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>168.17</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>166.18</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>167.93</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>1.64</v>
       </c>
     </row>
@@ -1003,19 +1041,19 @@
       <c r="A6">
         <v>20</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>170.02</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="3">
         <v>172.38</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>169.55</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>170.65</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3">
         <v>1.52</v>
       </c>
     </row>
@@ -1023,19 +1061,19 @@
       <c r="A7">
         <v>25</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>170.01</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>168.45</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>172.95</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>170.47</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="3">
         <v>2.2799999999999998</v>
       </c>
     </row>
@@ -1043,19 +1081,19 @@
       <c r="A8">
         <v>30</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>167.87</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>168.72</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>165.94</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <v>167.51</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="3">
         <v>1.42</v>
       </c>
     </row>
@@ -1063,19 +1101,19 @@
       <c r="A9">
         <v>35</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>171.45</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>173.13</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="3">
         <v>170.04</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="3">
         <v>171.54</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="3">
         <v>1.55</v>
       </c>
     </row>
@@ -1083,19 +1121,19 @@
       <c r="A10">
         <v>40</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>166.3</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>167.22</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="3">
         <v>169.34</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="3">
         <v>167.62</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="3">
         <v>1.56</v>
       </c>
     </row>
@@ -1103,19 +1141,19 @@
       <c r="A11">
         <v>45</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>167.63</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="3">
         <v>170.42</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="3">
         <v>170.12</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="3">
         <v>169.39</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="3">
         <v>1.53</v>
       </c>
     </row>
@@ -1123,40 +1161,40 @@
       <c r="A12">
         <v>50</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>166.48</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>166.93</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <v>168.82</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
         <v>167.41</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="3">
         <v>1.24</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" ht="14.25">
       <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>11</v>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1175,7 +1213,7 @@
       <c r="E16">
         <v>977.67</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="3">
         <v>3.19</v>
       </c>
     </row>
@@ -1195,7 +1233,7 @@
       <c r="E17">
         <v>978</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="3">
         <v>4.0599999999999996</v>
       </c>
     </row>
@@ -1215,7 +1253,7 @@
       <c r="E18">
         <v>980.67</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="3">
         <v>2.4900000000000002</v>
       </c>
     </row>
@@ -1235,7 +1273,7 @@
       <c r="E19">
         <v>976.67</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="3">
         <v>3.03</v>
       </c>
     </row>
@@ -1255,7 +1293,7 @@
       <c r="E20">
         <v>975</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="3">
         <v>2.92</v>
       </c>
     </row>
@@ -1275,7 +1313,7 @@
       <c r="E21">
         <v>979</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="3">
         <v>2.12</v>
       </c>
     </row>
@@ -1295,7 +1333,7 @@
       <c r="E22">
         <v>976</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="3">
         <v>3.16</v>
       </c>
     </row>
@@ -1315,7 +1353,7 @@
       <c r="E23">
         <v>978.67</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="3">
         <v>2.39</v>
       </c>
     </row>
@@ -1335,7 +1373,7 @@
       <c r="E24">
         <v>976.67</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="3">
         <v>2.86</v>
       </c>
     </row>
@@ -1355,7 +1393,7 @@
       <c r="E25">
         <v>981.33</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="3">
         <v>2.39</v>
       </c>
     </row>
@@ -1375,7 +1413,7 @@
       <c r="E26">
         <v>980.67</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="3">
         <v>1.3</v>
       </c>
     </row>
@@ -1388,36 +1426,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0C526B-3DF0-4F21-B71A-27E56F87F874}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="14.75" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
     <col min="3" max="3" width="22.25" customWidth="1"/>
     <col min="4" max="4" width="18.25" customWidth="1"/>
     <col min="5" max="5" width="13.25" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="20.58203125" customWidth="1"/>
-    <col min="8" max="8" width="16.58203125" customWidth="1"/>
+    <col min="7" max="7" width="20.625" customWidth="1"/>
+    <col min="8" max="8" width="16.625" customWidth="1"/>
     <col min="9" max="9" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="14.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1425,19 +1463,19 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>168.58</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>168.68</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>170.79</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>169.35</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>1.25</v>
       </c>
     </row>
@@ -1445,19 +1483,19 @@
       <c r="A3">
         <v>200</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>165.75</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>168.21</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>169.02</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>167.66</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>1.7</v>
       </c>
     </row>
@@ -1465,19 +1503,19 @@
       <c r="A4">
         <v>400</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>167.09</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>169.5</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>169.75</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>168.78</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>1.47</v>
       </c>
     </row>
@@ -1485,19 +1523,19 @@
       <c r="A5">
         <v>600</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>168.2</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>170.81</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>171.47</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>170.16</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>1.73</v>
       </c>
     </row>
@@ -1505,19 +1543,19 @@
       <c r="A6">
         <v>800</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>165.7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="3">
         <v>168.88</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>169.75</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>168.11</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3">
         <v>2.13</v>
       </c>
     </row>
@@ -1525,40 +1563,40 @@
       <c r="A7">
         <v>1000</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>168.39</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>168.85</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>171.11</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>169.45</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="3">
         <v>1.46</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" ht="14.25">
       <c r="A12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>11</v>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1690,14 +1728,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09D58A00-3ADD-4581-A42E-258E7C3FEED8}">
   <dimension ref="A1:B882"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2">

--- a/Source Data/Source Data Fig. 3.xlsx
+++ b/Source Data/Source Data Fig. 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nusu-my.sharepoint.com/personal/khudiyev_nus_edu_sg/Documents/PUBLICATIONS/PUBLISHED/Fiber Computer/Nature/Pre-Acceptance_Revision/Source Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nusu-my.sharepoint.com/personal/e1135497_u_nus_edu/Documents/Lab Document/Projects/Fiber display/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{548CC7E3-1D8D-410A-83F9-66C778B83176}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D0B2B0F-259F-420B-81E7-590299156380}"/>
   <bookViews>
-    <workbookView xWindow="4790" yWindow="4720" windowWidth="28800" windowHeight="15370" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9675" yWindow="8655" windowWidth="23370" windowHeight="11715" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 3d" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>Time (h)</t>
   </si>
@@ -109,7 +109,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="176" formatCode="0.00000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -167,7 +167,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -176,7 +176,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -192,9 +192,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -232,7 +232,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -338,7 +338,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -480,7 +480,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -489,7 +489,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="27.625" customWidth="1"/>
@@ -497,7 +497,7 @@
     <col min="5" max="5" width="24.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -510,7 +510,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="14.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="5"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -525,7 +525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>0</v>
       </c>
@@ -929,7 +929,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2728C3D7-42E8-48EC-A13E-D9FC52D07AAA}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
     <col min="2" max="2" width="16.625" customWidth="1"/>
@@ -937,7 +937,7 @@
     <col min="4" max="4" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -950,12 +950,6 @@
       <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
@@ -970,12 +964,8 @@
       <c r="D2" s="3">
         <v>171.08</v>
       </c>
-      <c r="E2" s="3">
-        <v>171.55</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1.37</v>
-      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
@@ -990,12 +980,8 @@
       <c r="D3" s="3">
         <v>171.75</v>
       </c>
-      <c r="E3" s="3">
-        <v>169.8</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1.95</v>
-      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
@@ -1010,12 +996,8 @@
       <c r="D4" s="3">
         <v>172.38</v>
       </c>
-      <c r="E4" s="3">
-        <v>169.91</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2.14</v>
-      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
@@ -1030,12 +1012,8 @@
       <c r="D5" s="3">
         <v>166.18</v>
       </c>
-      <c r="E5" s="3">
-        <v>167.93</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1.64</v>
-      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
@@ -1050,12 +1028,8 @@
       <c r="D6" s="3">
         <v>169.55</v>
       </c>
-      <c r="E6" s="3">
-        <v>170.65</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1.52</v>
-      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
@@ -1070,12 +1044,8 @@
       <c r="D7" s="3">
         <v>172.95</v>
       </c>
-      <c r="E7" s="3">
-        <v>170.47</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2.2799999999999998</v>
-      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
@@ -1090,12 +1060,8 @@
       <c r="D8" s="3">
         <v>165.94</v>
       </c>
-      <c r="E8" s="3">
-        <v>167.51</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1.42</v>
-      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
@@ -1110,12 +1076,8 @@
       <c r="D9" s="3">
         <v>170.04</v>
       </c>
-      <c r="E9" s="3">
-        <v>171.54</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1.55</v>
-      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
@@ -1130,12 +1092,8 @@
       <c r="D10" s="3">
         <v>169.34</v>
       </c>
-      <c r="E10" s="3">
-        <v>167.62</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1.56</v>
-      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
@@ -1150,12 +1108,8 @@
       <c r="D11" s="3">
         <v>170.12</v>
       </c>
-      <c r="E11" s="3">
-        <v>169.39</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1.53</v>
-      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
@@ -1170,14 +1124,10 @@
       <c r="D12" s="3">
         <v>168.82</v>
       </c>
-      <c r="E12" s="3">
-        <v>167.41</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="14.25">
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1190,12 +1140,6 @@
       <c r="D15" t="s">
         <v>14</v>
       </c>
-      <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
@@ -1210,12 +1154,7 @@
       <c r="D16">
         <v>979</v>
       </c>
-      <c r="E16">
-        <v>977.67</v>
-      </c>
-      <c r="F16" s="3">
-        <v>3.19</v>
-      </c>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
@@ -1230,12 +1169,7 @@
       <c r="D17">
         <v>974</v>
       </c>
-      <c r="E17">
-        <v>978</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4.0599999999999996</v>
-      </c>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
@@ -1250,12 +1184,7 @@
       <c r="D18">
         <v>982</v>
       </c>
-      <c r="E18">
-        <v>980.67</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2.4900000000000002</v>
-      </c>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
@@ -1270,12 +1199,7 @@
       <c r="D19">
         <v>973</v>
       </c>
-      <c r="E19">
-        <v>976.67</v>
-      </c>
-      <c r="F19" s="3">
-        <v>3.03</v>
-      </c>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
@@ -1290,12 +1214,7 @@
       <c r="D20">
         <v>972</v>
       </c>
-      <c r="E20">
-        <v>975</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2.92</v>
-      </c>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
@@ -1310,12 +1229,7 @@
       <c r="D21">
         <v>979</v>
       </c>
-      <c r="E21">
-        <v>979</v>
-      </c>
-      <c r="F21" s="3">
-        <v>2.12</v>
-      </c>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
@@ -1330,12 +1244,7 @@
       <c r="D22">
         <v>973</v>
       </c>
-      <c r="E22">
-        <v>976</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3.16</v>
-      </c>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
@@ -1350,12 +1259,7 @@
       <c r="D23">
         <v>979</v>
       </c>
-      <c r="E23">
-        <v>978.67</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2.39</v>
-      </c>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
@@ -1370,12 +1274,7 @@
       <c r="D24">
         <v>975</v>
       </c>
-      <c r="E24">
-        <v>976.67</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2.86</v>
-      </c>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
@@ -1390,12 +1289,7 @@
       <c r="D25">
         <v>979</v>
       </c>
-      <c r="E25">
-        <v>981.33</v>
-      </c>
-      <c r="F25" s="3">
-        <v>2.39</v>
-      </c>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
@@ -1410,12 +1304,7 @@
       <c r="D26">
         <v>980</v>
       </c>
-      <c r="E26">
-        <v>980.67</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1.3</v>
-      </c>
+      <c r="F26" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1426,7 +1315,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0C526B-3DF0-4F21-B71A-27E56F87F874}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.75" customWidth="1"/>
     <col min="2" max="2" width="15.875" customWidth="1"/>
@@ -1439,7 +1328,7 @@
     <col min="9" max="9" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -1579,7 +1468,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14.25">
+    <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -1728,7 +1617,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09D58A00-3ADD-4581-A42E-258E7C3FEED8}">
   <dimension ref="A1:B882"/>
-  <sheetFormatPr defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">

--- a/Source Data/Source Data Fig. 3.xlsx
+++ b/Source Data/Source Data Fig. 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nusu-my.sharepoint.com/personal/e1135497_u_nus_edu/Documents/Lab Document/Projects/Fiber display/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D0B2B0F-259F-420B-81E7-590299156380}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{987204B8-773D-493A-A19E-7A26C4F3CEB8}"/>
   <bookViews>
-    <workbookView xWindow="9675" yWindow="8655" windowWidth="23370" windowHeight="11715" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9105" yWindow="8520" windowWidth="23370" windowHeight="11715" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 3d" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>Time (h)</t>
   </si>
@@ -98,10 +98,11 @@
     <t>Bending cycles</t>
   </si>
   <si>
-    <t>Time (us)</t>
+    <t>Voltage (V)</t>
   </si>
   <si>
-    <t>Voltage (V)</t>
+    <t>Time (μs)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -189,6 +190,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -928,7 +933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2728C3D7-42E8-48EC-A13E-D9FC52D07AAA}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
@@ -1127,184 +1132,184 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
-        <v>14</v>
-      </c>
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <v>974</v>
+      </c>
+      <c r="C15">
+        <v>980</v>
+      </c>
+      <c r="D15">
+        <v>979</v>
+      </c>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B16">
+        <v>982</v>
+      </c>
+      <c r="C16">
+        <v>978</v>
+      </c>
+      <c r="D16">
         <v>974</v>
-      </c>
-      <c r="C16">
-        <v>980</v>
-      </c>
-      <c r="D16">
-        <v>979</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B17">
+        <v>978</v>
+      </c>
+      <c r="C17">
         <v>982</v>
       </c>
-      <c r="C17">
-        <v>978</v>
-      </c>
       <c r="D17">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B18">
+        <v>979</v>
+      </c>
+      <c r="C18">
         <v>978</v>
       </c>
-      <c r="C18">
-        <v>982</v>
-      </c>
       <c r="D18">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B19">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="C19">
         <v>978</v>
       </c>
       <c r="D19">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B20">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="C20">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D20">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B21">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C21">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D21">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B22">
+        <v>976</v>
+      </c>
+      <c r="C22">
+        <v>981</v>
+      </c>
+      <c r="D22">
         <v>979</v>
-      </c>
-      <c r="C22">
-        <v>976</v>
-      </c>
-      <c r="D22">
-        <v>973</v>
       </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B23">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C23">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="D23">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B24">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="C24">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="D24">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B25">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C25">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="D25">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>50</v>
-      </c>
-      <c r="B26">
-        <v>980</v>
-      </c>
-      <c r="C26">
-        <v>982</v>
-      </c>
-      <c r="D26">
-        <v>980</v>
-      </c>
-      <c r="F26" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1314,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0C526B-3DF0-4F21-B71A-27E56F87F874}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.75" customWidth="1"/>
@@ -1328,7 +1333,7 @@
     <col min="9" max="9" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -1347,8 +1352,23 @@
       <c r="F1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1367,8 +1387,23 @@
       <c r="F2" s="3">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>989</v>
+      </c>
+      <c r="H2">
+        <v>986</v>
+      </c>
+      <c r="I2">
+        <v>986</v>
+      </c>
+      <c r="J2">
+        <v>987</v>
+      </c>
+      <c r="K2">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>200</v>
       </c>
@@ -1387,8 +1422,23 @@
       <c r="F3" s="3">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>995</v>
+      </c>
+      <c r="H3">
+        <v>997</v>
+      </c>
+      <c r="I3">
+        <v>998</v>
+      </c>
+      <c r="J3">
+        <v>996.67</v>
+      </c>
+      <c r="K3">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>400</v>
       </c>
@@ -1407,8 +1457,23 @@
       <c r="F4" s="3">
         <v>1.47</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <v>1004</v>
+      </c>
+      <c r="H4">
+        <v>999</v>
+      </c>
+      <c r="I4">
+        <v>1006</v>
+      </c>
+      <c r="J4">
+        <v>1003</v>
+      </c>
+      <c r="K4">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>600</v>
       </c>
@@ -1427,8 +1492,23 @@
       <c r="F5" s="3">
         <v>1.73</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>1001</v>
+      </c>
+      <c r="H5">
+        <v>1004</v>
+      </c>
+      <c r="I5">
+        <v>1004</v>
+      </c>
+      <c r="J5">
+        <v>1003</v>
+      </c>
+      <c r="K5">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>800</v>
       </c>
@@ -1447,8 +1527,23 @@
       <c r="F6" s="3">
         <v>2.13</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>1009</v>
+      </c>
+      <c r="H6">
+        <v>1010</v>
+      </c>
+      <c r="I6">
+        <v>1005</v>
+      </c>
+      <c r="J6">
+        <v>1008</v>
+      </c>
+      <c r="K6">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -1467,144 +1562,19 @@
       <c r="F7" s="3">
         <v>1.46</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>0</v>
-      </c>
-      <c r="B13">
-        <v>989</v>
-      </c>
-      <c r="C13">
-        <v>986</v>
-      </c>
-      <c r="D13">
-        <v>986</v>
-      </c>
-      <c r="E13">
-        <v>987</v>
-      </c>
-      <c r="F13">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>200</v>
-      </c>
-      <c r="B14">
-        <v>995</v>
-      </c>
-      <c r="C14">
-        <v>997</v>
-      </c>
-      <c r="D14">
-        <v>998</v>
-      </c>
-      <c r="E14">
-        <v>996.67</v>
-      </c>
-      <c r="F14">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>400</v>
-      </c>
-      <c r="B15">
-        <v>1004</v>
-      </c>
-      <c r="C15">
-        <v>999</v>
-      </c>
-      <c r="D15">
+      <c r="G7">
+        <v>1005</v>
+      </c>
+      <c r="H7">
+        <v>1012</v>
+      </c>
+      <c r="I7">
         <v>1006</v>
       </c>
-      <c r="E15">
-        <v>1003</v>
-      </c>
-      <c r="F15">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>600</v>
-      </c>
-      <c r="B16">
-        <v>1001</v>
-      </c>
-      <c r="C16">
-        <v>1004</v>
-      </c>
-      <c r="D16">
-        <v>1004</v>
-      </c>
-      <c r="E16">
-        <v>1003</v>
-      </c>
-      <c r="F16">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>800</v>
-      </c>
-      <c r="B17">
-        <v>1009</v>
-      </c>
-      <c r="C17">
-        <v>1010</v>
-      </c>
-      <c r="D17">
-        <v>1005</v>
-      </c>
-      <c r="E17">
-        <v>1008</v>
-      </c>
-      <c r="F17">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>1000</v>
-      </c>
-      <c r="B18">
-        <v>1005</v>
-      </c>
-      <c r="C18">
-        <v>1012</v>
-      </c>
-      <c r="D18">
-        <v>1006</v>
-      </c>
-      <c r="E18">
+      <c r="J7">
         <v>1007.67</v>
       </c>
-      <c r="F18">
+      <c r="K7">
         <v>3.79</v>
       </c>
     </row>
@@ -1621,10 +1591,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2">

--- a/Source Data/Source Data Fig. 3.xlsx
+++ b/Source Data/Source Data Fig. 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nusu-my.sharepoint.com/personal/e1135497_u_nus_edu/Documents/Lab Document/Projects/Fiber display/documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nusu-my.sharepoint.com/personal/khudiyev_nus_edu_sg/Documents/PUBLICATIONS/PUBLISHED/Fiber Computer/Nature/Pre-Acceptance_Revision/uploaded/Source Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{987204B8-773D-493A-A19E-7A26C4F3CEB8}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34DC7A2F-B998-5B43-A5BE-C2F2A96FE986}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="8520" windowWidth="23370" windowHeight="11715" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9100" yWindow="8080" windowWidth="23380" windowHeight="11720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 3d" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Time (h)</t>
   </si>
@@ -74,12 +74,6 @@
     <t>Illuminance 3 (lux)</t>
   </si>
   <si>
-    <t>Mean (lux)</t>
-  </si>
-  <si>
-    <t>SD (lux)</t>
-  </si>
-  <si>
     <t>Resistance 1 (kΩ)</t>
   </si>
   <si>
@@ -89,20 +83,26 @@
     <t>Resistance 3 (kΩ)</t>
   </si>
   <si>
+    <t>Bending cycles</t>
+  </si>
+  <si>
+    <t>Mean (lux)</t>
+  </si>
+  <si>
+    <t>SD (lux)</t>
+  </si>
+  <si>
     <t>Mean (kΩ)</t>
   </si>
   <si>
     <t>SD (kΩ)</t>
   </si>
   <si>
-    <t>Bending cycles</t>
+    <t>Time (μs)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Voltage (V)</t>
-  </si>
-  <si>
-    <t>Time (μs)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -494,12 +494,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="27.625" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
     <col min="4" max="4" width="22.5" customWidth="1"/>
-    <col min="5" max="5" width="24.125" customWidth="1"/>
+    <col min="5" max="5" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -933,16 +933,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2728C3D7-42E8-48EC-A13E-D9FC52D07AAA}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.25" customWidth="1"/>
-    <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="3" width="19.875" customWidth="1"/>
-    <col min="4" max="4" width="24.625" customWidth="1"/>
+    <col min="1" max="1" width="16.1640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -955,8 +955,17 @@
       <c r="D1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -969,10 +978,17 @@
       <c r="D2" s="3">
         <v>171.08</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="E2">
+        <v>974</v>
+      </c>
+      <c r="F2">
+        <v>980</v>
+      </c>
+      <c r="G2">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>5</v>
       </c>
@@ -985,10 +1001,17 @@
       <c r="D3" s="3">
         <v>171.75</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="E3">
+        <v>982</v>
+      </c>
+      <c r="F3">
+        <v>978</v>
+      </c>
+      <c r="G3">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>10</v>
       </c>
@@ -1001,10 +1024,17 @@
       <c r="D4" s="3">
         <v>172.38</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="E4">
+        <v>978</v>
+      </c>
+      <c r="F4">
+        <v>982</v>
+      </c>
+      <c r="G4">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>15</v>
       </c>
@@ -1017,10 +1047,17 @@
       <c r="D5" s="3">
         <v>166.18</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="E5">
+        <v>979</v>
+      </c>
+      <c r="F5">
+        <v>978</v>
+      </c>
+      <c r="G5">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>20</v>
       </c>
@@ -1033,10 +1070,17 @@
       <c r="D6" s="3">
         <v>169.55</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="E6">
+        <v>975</v>
+      </c>
+      <c r="F6">
+        <v>978</v>
+      </c>
+      <c r="G6">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>25</v>
       </c>
@@ -1049,10 +1093,17 @@
       <c r="D7" s="3">
         <v>172.95</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="E7">
+        <v>981</v>
+      </c>
+      <c r="F7">
+        <v>977</v>
+      </c>
+      <c r="G7">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>30</v>
       </c>
@@ -1065,10 +1116,17 @@
       <c r="D8" s="3">
         <v>165.94</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="E8">
+        <v>979</v>
+      </c>
+      <c r="F8">
+        <v>976</v>
+      </c>
+      <c r="G8">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>35</v>
       </c>
@@ -1081,10 +1139,17 @@
       <c r="D9" s="3">
         <v>170.04</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="E9">
+        <v>976</v>
+      </c>
+      <c r="F9">
+        <v>981</v>
+      </c>
+      <c r="G9">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>40</v>
       </c>
@@ -1097,10 +1162,17 @@
       <c r="D10" s="3">
         <v>169.34</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="E10">
+        <v>975</v>
+      </c>
+      <c r="F10">
+        <v>980</v>
+      </c>
+      <c r="G10">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>45</v>
       </c>
@@ -1113,10 +1185,17 @@
       <c r="D11" s="3">
         <v>170.12</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="E11">
+        <v>981</v>
+      </c>
+      <c r="F11">
+        <v>984</v>
+      </c>
+      <c r="G11">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>50</v>
       </c>
@@ -1129,187 +1208,15 @@
       <c r="D12" s="3">
         <v>168.82</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>0</v>
-      </c>
-      <c r="B15">
-        <v>974</v>
-      </c>
-      <c r="C15">
+      <c r="E12">
         <v>980</v>
       </c>
-      <c r="D15">
-        <v>979</v>
-      </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
+      <c r="F12">
         <v>982</v>
       </c>
-      <c r="C16">
-        <v>978</v>
-      </c>
-      <c r="D16">
-        <v>974</v>
-      </c>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>10</v>
-      </c>
-      <c r="B17">
-        <v>978</v>
-      </c>
-      <c r="C17">
-        <v>982</v>
-      </c>
-      <c r="D17">
-        <v>982</v>
-      </c>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>15</v>
-      </c>
-      <c r="B18">
-        <v>979</v>
-      </c>
-      <c r="C18">
-        <v>978</v>
-      </c>
-      <c r="D18">
-        <v>973</v>
-      </c>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20</v>
-      </c>
-      <c r="B19">
-        <v>975</v>
-      </c>
-      <c r="C19">
-        <v>978</v>
-      </c>
-      <c r="D19">
-        <v>972</v>
-      </c>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>25</v>
-      </c>
-      <c r="B20">
-        <v>981</v>
-      </c>
-      <c r="C20">
-        <v>977</v>
-      </c>
-      <c r="D20">
-        <v>979</v>
-      </c>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>30</v>
-      </c>
-      <c r="B21">
-        <v>979</v>
-      </c>
-      <c r="C21">
-        <v>976</v>
-      </c>
-      <c r="D21">
-        <v>973</v>
-      </c>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>35</v>
-      </c>
-      <c r="B22">
-        <v>976</v>
-      </c>
-      <c r="C22">
-        <v>981</v>
-      </c>
-      <c r="D22">
-        <v>979</v>
-      </c>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>40</v>
-      </c>
-      <c r="B23">
-        <v>975</v>
-      </c>
-      <c r="C23">
+      <c r="G12">
         <v>980</v>
       </c>
-      <c r="D23">
-        <v>975</v>
-      </c>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>45</v>
-      </c>
-      <c r="B24">
-        <v>981</v>
-      </c>
-      <c r="C24">
-        <v>984</v>
-      </c>
-      <c r="D24">
-        <v>979</v>
-      </c>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>50</v>
-      </c>
-      <c r="B25">
-        <v>980</v>
-      </c>
-      <c r="C25">
-        <v>982</v>
-      </c>
-      <c r="D25">
-        <v>980</v>
-      </c>
-      <c r="F25" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1320,22 +1227,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0C526B-3DF0-4F21-B71A-27E56F87F874}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.75" customWidth="1"/>
-    <col min="2" max="2" width="15.875" customWidth="1"/>
-    <col min="3" max="3" width="22.25" customWidth="1"/>
-    <col min="4" max="4" width="18.25" customWidth="1"/>
-    <col min="5" max="5" width="13.25" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="20.625" customWidth="1"/>
-    <col min="8" max="8" width="16.625" customWidth="1"/>
-    <col min="9" max="9" width="18.25" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
@@ -1347,25 +1254,25 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
       <c r="J1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1587,14 +1494,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09D58A00-3ADD-4581-A42E-258E7C3FEED8}">
   <dimension ref="A1:B882"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2">
